--- a/data/trans_camb/P19C06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,24</t>
+          <t>-1,67; 2,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,04</t>
+          <t>-1,56; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,45</t>
+          <t>-2,52; 0,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,28</t>
+          <t>-2,33; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,25</t>
+          <t>-2,45; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,9</t>
+          <t>-2,01; 1,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,61</t>
+          <t>-1,42; 1,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,58</t>
+          <t>-1,46; 1,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,83</t>
+          <t>-1,69; 0,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-85,73; 483,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,12; 506,81</t>
+          <t>-77,01; 471,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 176,22</t>
+          <t>-100,0; 145,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 282,28</t>
+          <t>-76,3; 289,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,57; 349,14</t>
+          <t>-79,17; 322,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,77; 254,12</t>
+          <t>-60,83; 265,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,2; 172,44</t>
+          <t>-63,04; 161,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 186,03</t>
+          <t>-67,06; 158,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 108,2</t>
+          <t>-66,87; 92,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,67</t>
+          <t>-2,3; 0,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,7</t>
+          <t>-2,48; 0,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 0,65</t>
+          <t>-2,28; 0,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,83</t>
+          <t>-0,55; 3,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,65</t>
+          <t>-1,48; 1,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,48</t>
+          <t>-2,18; 0,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,61</t>
+          <t>-0,96; 1,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,9</t>
+          <t>-1,39; 0,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,33</t>
+          <t>-1,69; 0,28</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 302,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,37 +1009,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>-94,53; 250,06</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-49,25; 954,92</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>-91,8; 417,29</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-61,38; 1064,98</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 184,96</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 274,03</t>
+          <t>-58,9; 259,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 175,86</t>
+          <t>-79,45; 138,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,44; 79,15</t>
+          <t>-81,76; 60,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,85</t>
+          <t>-1,6; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,06</t>
+          <t>-1,57; 1,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,39</t>
+          <t>-2,57; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,03</t>
+          <t>-2,03; 3,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,0</t>
+          <t>-4,41; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,23</t>
+          <t>-4,41; 0,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,09</t>
+          <t>-1,0; 2,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,18</t>
+          <t>-1,76; 1,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,11</t>
+          <t>-2,31; 0,16</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,17; 198,24</t>
+          <t>-62,1; 190,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,8; 247,46</t>
+          <t>-69,97; 288,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-93,17; 39,31</t>
+          <t>-92,96; 45,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,11; 229,6</t>
+          <t>-43,61; 231,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 138,41</t>
+          <t>-76,94; 129,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 24,64</t>
+          <t>-90,67; 14,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,13</t>
+          <t>-1,62; 0,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,59</t>
+          <t>-1,53; 0,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,32</t>
+          <t>-1,16; 1,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,08</t>
+          <t>-1,13; 1,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,71</t>
+          <t>-0,65; 1,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,88</t>
+          <t>-1,36; 0,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,34</t>
+          <t>-1,07; 0,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,88</t>
+          <t>-0,75; 0,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,71</t>
+          <t>-0,99; 0,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,62; 36,64</t>
+          <t>-89,09; 62,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,49; 96,3</t>
+          <t>-87,12; 108,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-77,47; 220,8</t>
+          <t>-78,61; 281,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 278,92</t>
+          <t>-75,62; 299,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,25; 329,91</t>
+          <t>-50,49; 348,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 152,41</t>
+          <t>-74,2; 210,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,31; 54,89</t>
+          <t>-71,13; 44,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 132,53</t>
+          <t>-52,73; 109,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 86,27</t>
+          <t>-62,21; 93,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,35</t>
+          <t>0,25; 2,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,66</t>
+          <t>0,71; 3,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,98</t>
+          <t>0,14; 1,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,29</t>
+          <t>-1,23; 1,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,15</t>
+          <t>-1,47; 1,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,34</t>
+          <t>-1,18; 1,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,31</t>
+          <t>-0,53; 1,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,6</t>
+          <t>-0,35; 1,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,13</t>
+          <t>-0,56; 1,21</t>
         </is>
       </c>
     </row>
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 246,01</t>
+          <t>-68,93; 199,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 259,57</t>
+          <t>-76,59; 231,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,96; 260,75</t>
+          <t>-54,6; 243,97</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,48; 501,72</t>
+          <t>-49,99; 347,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 428,22</t>
+          <t>-36,46; 434,97</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-42,72; 311,13</t>
+          <t>-43,95; 342,8</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,18</t>
+          <t>-0,68; 1,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,57</t>
+          <t>-0,5; 1,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,41</t>
+          <t>-1,17; 0,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,07</t>
+          <t>-0,45; 1,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,41</t>
+          <t>-0,35; 1,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,69</t>
+          <t>-0,8; 0,62</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 276,48</t>
+          <t>-52,49; 248,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 312,86</t>
+          <t>-47,18; 300,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 139,95</t>
+          <t>-85,77; 173,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-53,72; 241,31</t>
+          <t>-49,62; 303,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-33,67; 360,98</t>
+          <t>-35,95; 332,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 213,85</t>
+          <t>-76,49; 215,52</t>
         </is>
       </c>
     </row>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,72</t>
+          <t>-0,51; 0,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,34</t>
+          <t>-0,86; 0,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,91</t>
+          <t>-0,32; 0,93</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,75</t>
+          <t>-0,39; 0,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,4</t>
+          <t>-0,63; 0,39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,48</t>
+          <t>-0,32; 0,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,59</t>
+          <t>-0,24; 0,6</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,21</t>
+          <t>-0,61; 0,2</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-48,59; 57,69</t>
+          <t>-49,41; 52,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 87,75</t>
+          <t>-37,07; 83,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-62,22; 45,55</t>
+          <t>-61,7; 41,23</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 108,9</t>
+          <t>-22,73; 102,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,83; 83,48</t>
+          <t>-27,29; 88,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 46,04</t>
+          <t>-41,23; 47,62</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 51,26</t>
+          <t>-23,52; 55,67</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 65,58</t>
+          <t>-19,33; 65,26</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 20,83</t>
+          <t>-43,92; 23,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Clase-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,33</t>
+          <t>-1,67; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,21</t>
+          <t>-1,65; 2,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,37</t>
+          <t>-2,49; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,25</t>
+          <t>-2,19; 2,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,25</t>
+          <t>-2,51; 2,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,91</t>
+          <t>-2,28; 1,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,46</t>
+          <t>-1,24; 1,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,47</t>
+          <t>-1,32; 1,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,77</t>
+          <t>-1,79; 0,72</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-54,91%</t>
+          <t>-55,05%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,58%</t>
+          <t>-22,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,33; 567,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-77,01; 471,4</t>
+          <t>-77,13; 478,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 145,71</t>
+          <t>-100,0; 162,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,3; 289,88</t>
+          <t>-74,91; 345,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 322,16</t>
+          <t>-84,3; 319,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,83; 265,96</t>
+          <t>-65,14; 287,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,04; 161,3</t>
+          <t>-56,06; 191,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 158,86</t>
+          <t>-59,18; 193,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,87; 92,75</t>
+          <t>-68,95; 81,58</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,75</t>
+          <t>-2,34; 0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,62</t>
+          <t>-2,28; 0,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,68</t>
+          <t>-2,48; 0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,86</t>
+          <t>-0,85; 3,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,65</t>
+          <t>-1,45; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,45</t>
+          <t>-2,24; 0,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,58</t>
+          <t>-0,99; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,83</t>
+          <t>-1,4; 0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,28</t>
+          <t>-1,67; 0,22</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-42,07%</t>
+          <t>-44,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-47,28%</t>
+          <t>-49,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,99%</t>
+          <t>-46,5%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 226,59</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 213,7</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-94,53; 250,06</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 954,92</t>
+          <t>-62,53; 867,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,8; 417,29</t>
+          <t>-85,51; 427,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,72; 138,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,9; 259,25</t>
+          <t>-59,53; 205,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 138,55</t>
+          <t>-81,19; 156,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 60,49</t>
+          <t>-82,32; 43,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,83</t>
+          <t>-1,53; 1,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,91</t>
+          <t>-1,75; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,42</t>
+          <t>-2,24; 0,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,85</t>
+          <t>-1,68; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,0</t>
+          <t>-4,44; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 0,33</t>
+          <t>-4,64; 0,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,06</t>
+          <t>-1,08; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,14</t>
+          <t>-1,82; 1,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,16</t>
+          <t>-2,11; 0,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-54,03%</t>
+          <t>-36,63%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-77,91%</t>
+          <t>-52,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-57,96%</t>
+          <t>-41,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,1; 190,07</t>
+          <t>-60,35; 242,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 288,18</t>
+          <t>-75,06; 232,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-92,96; 45,57</t>
+          <t>-84,08; 107,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>-78,55; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 231,01</t>
+          <t>-45,37; 222,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,94; 129,35</t>
+          <t>-77,08; 140,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 14,0</t>
+          <t>-79,04; 74,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,21</t>
+          <t>-1,62; 0,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,66</t>
+          <t>-1,5; 0,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,42</t>
+          <t>-1,53; 0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,13</t>
+          <t>-1,13; 1,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,74</t>
+          <t>-0,58; 1,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,93</t>
+          <t>-0,89; 1,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,26</t>
+          <t>-1,03; 0,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,77</t>
+          <t>-0,82; 0,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,68</t>
+          <t>-0,86; 0,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,2%</t>
+          <t>-39,96%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,09%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,13%</t>
+          <t>-19,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,09; 62,71</t>
+          <t>-90,16; 32,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-87,12; 108,29</t>
+          <t>-85,73; 86,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 281,62</t>
+          <t>-84,6; 91,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-75,62; 299,37</t>
+          <t>-72,72; 217,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,49; 348,01</t>
+          <t>-40,36; 412,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 210,02</t>
+          <t>-61,93; 275,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 44,87</t>
+          <t>-69,6; 43,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 109,55</t>
+          <t>-52,87; 100,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-62,21; 93,73</t>
+          <t>-57,56; 91,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,39</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,53</t>
+          <t>0,71; 3,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,99</t>
+          <t>0,12; 1,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,21</t>
+          <t>-1,37; 1,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,21</t>
+          <t>-1,47; 1,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,28</t>
+          <t>-0,98; 1,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,29</t>
+          <t>-0,49; 1,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,62</t>
+          <t>-0,25; 1,82</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,21</t>
+          <t>-0,47; 1,24</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -1662,39 +1662,39 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,93; 199,69</t>
+          <t>-72,17; 197,82</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 231,35</t>
+          <t>-79,27; 219,41</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,6; 243,97</t>
+          <t>-48,22; 315,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 347,83</t>
+          <t>-45,09; 384,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 434,97</t>
+          <t>-28,58; 546,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 342,8</t>
+          <t>-38,21; 349,91</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,15</t>
+          <t>-0,67; 1,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,53</t>
+          <t>-0,58; 1,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,42</t>
+          <t>-1,35; -0,01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,15</t>
+          <t>-0,47; 1,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,33</t>
+          <t>-0,29; 1,43</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,62</t>
+          <t>-0,93; 0,33</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-44,78%</t>
+          <t>-64,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-15,96%</t>
+          <t>-37,14%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 248,87</t>
+          <t>-61,35; 255,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 300,12</t>
+          <t>-50,49; 354,5</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,77; 173,29</t>
+          <t>-91,9; 28,32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 303,81</t>
+          <t>-46,84; 258,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,95; 332,63</t>
+          <t>-35,97; 345,6</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 215,52</t>
+          <t>-81,89; 144,9</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,44</t>
+          <t>-0,69; 0,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,72</t>
+          <t>-0,53; 0,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,28</t>
+          <t>-0,89; 0,15</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,93</t>
+          <t>-0,27; 0,89</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,77</t>
+          <t>-0,41; 0,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,39</t>
+          <t>-0,6; 0,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,53</t>
+          <t>-0,31; 0,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,6</t>
+          <t>-0,29; 0,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,2</t>
+          <t>-0,57; 0,14</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-25,77%</t>
+          <t>-31,44%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,76%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-15,85%</t>
+          <t>-16,64%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-49,41; 52,6</t>
+          <t>-49,13; 55,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 83,64</t>
+          <t>-38,75; 87,38</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-61,7; 41,23</t>
+          <t>-61,4; 22,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,73; 102,97</t>
+          <t>-20,07; 102,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 88,39</t>
+          <t>-28,68; 108,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 47,62</t>
+          <t>-41,32; 53,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 55,67</t>
+          <t>-23,31; 52,55</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,33; 65,26</t>
+          <t>-22,28; 60,89</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 23,09</t>
+          <t>-40,97; 16,66</t>
         </is>
       </c>
     </row>
